--- a/invoice_automation/clients/northsky_comm/templates/North Sky Vendor Invoice (Master).xlsx
+++ b/invoice_automation/clients/northsky_comm/templates/North Sky Vendor Invoice (Master).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PYTHON\PDFInvoiceExtract\invoice_automation\clients\northsky_comm\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A296C807-B9BB-49E0-B6D8-90F14679F9B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB88445E-4B2A-4A08-87A0-AFBDC8300DE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9510" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="205">
   <si>
     <t>Invoice Number</t>
   </si>
@@ -38,9 +38,6 @@
     <t>Invoice Amount</t>
   </si>
   <si>
-    <t>PO Reference (If only Contract ID, end with -)</t>
-  </si>
-  <si>
     <t>Contract ID (Intermediary Formula)</t>
   </si>
   <si>
@@ -92,24 +89,12 @@
     <t>Anna Dejeu</t>
   </si>
   <si>
-    <t>WA0 - Washington</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>Need PO Created</t>
-  </si>
-  <si>
     <t>Chanh Saephanh</t>
   </si>
   <si>
     <t>Latrice Farr</t>
   </si>
   <si>
-    <t>829151-Robert Michael Thoman</t>
-  </si>
-  <si>
     <t>Lori Paschall</t>
   </si>
   <si>
@@ -119,28 +104,7 @@
     <t>Samuel Elliot</t>
   </si>
   <si>
-    <t>21300</t>
-  </si>
-  <si>
-    <t>4600-LUMEN NE</t>
-  </si>
-  <si>
     <t>Josh Fitts</t>
-  </si>
-  <si>
-    <t>S32171</t>
-  </si>
-  <si>
-    <t>ARROW CONSTRUCTION SUPPLY - V02081</t>
-  </si>
-  <si>
-    <t>B21300-001358</t>
-  </si>
-  <si>
-    <t>B21300</t>
-  </si>
-  <si>
-    <t>001358</t>
   </si>
   <si>
     <t>Row 31</t>
@@ -671,17 +635,16 @@
   </si>
   <si>
     <t>05/28/26 12:54 PM</t>
+  </si>
+  <si>
+    <t>PO Reference</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="mm/dd/yy"/>
-    <numFmt numFmtId="165" formatCode="[$$-409]#,##0.00;\-[$$-409]#,##0.00"/>
-  </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -726,36 +689,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2E8DE"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -770,31 +710,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -1134,7 +1065,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:V2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -1143,7 +1074,7 @@
     <col min="4" max="4" width="15.54296875" customWidth="1"/>
     <col min="5" max="5" width="13.81640625" customWidth="1"/>
     <col min="6" max="6" width="19.26953125" customWidth="1"/>
-    <col min="7" max="7" width="8" hidden="1"/>
+    <col min="7" max="7" width="8.90625" customWidth="1"/>
     <col min="8" max="8" width="11.7265625" customWidth="1"/>
     <col min="9" max="9" width="10.453125" customWidth="1"/>
     <col min="10" max="10" width="13.81640625" customWidth="1"/>
@@ -1177,136 +1108,80 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
-        <v>21</v>
-      </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" s="3">
-        <v>46170</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D2" s="3">
-        <v>46163</v>
-      </c>
-      <c r="E2" s="5">
-        <v>254.4</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="L2" s="7"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="O2" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4">
-        <v>0</v>
-      </c>
-      <c r="V2" s="4"/>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A3" s="2"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
-      <c r="T3" s="4"/>
-      <c r="U3" s="4"/>
-      <c r="V3" s="4"/>
+      <c r="A2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1326,951 +1201,951 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="C1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D1" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B8" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B11" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B15" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D15" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C16" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D16" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="B19" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C19" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D19" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="B22" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C22" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D22" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="B25" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C25" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D25" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="C26" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D26" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="B29" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C29" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D29" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="B32" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C32" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D32" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="B35" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="C35" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D35" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="B38" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="C38" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D38" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="B41" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="C41" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D41" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="B44" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C44" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D44" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="B47" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="C47" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D47" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="B50" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="C50" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D50" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="B53" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="C53" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D53" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B54" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="C54" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D54" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="B57" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="C57" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D57" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="B60" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="C60" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D60" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="B63" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="C63" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="D63" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="B66" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="C66" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="D66" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="B69" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="C69" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D69" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="B72" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="C72" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D72" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="B75" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="C75" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="D75" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="B78" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="C78" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D78" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B79" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="C79" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="D79" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="B82" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="C82" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D82" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="B85" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="C85" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="D85" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="B88" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="C88" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D88" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="B91" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C91" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D91" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="B94" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="C94" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D94" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="B97" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="C97" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D97" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B98" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="C98" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="D98" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="B101" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="C101" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D101" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="B104" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="C104" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D104" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="B107" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="C107" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D107" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="B110" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="C110" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D110" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="B113" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="C113" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D113" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B114" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="C114" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="D114" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="B117" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="C117" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D117" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="B120" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="C120" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D120" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B121" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="C121" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D121" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="B124" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="C124" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D124" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="B127" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="C127" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D127" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="B130" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="C130" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D130" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="B133" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="C133" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D133" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="B136" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="C136" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D136" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B137" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="C137" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D137" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="B140" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="C140" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D140" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B141" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="C141" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="D141" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="B144" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="C144" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D144" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B145" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="C145" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="D145" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="B148" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="C148" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D148" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="B151" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C151" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D151" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="B154" t="s">
+        <v>167</v>
+      </c>
+      <c r="C154" t="s">
+        <v>25</v>
+      </c>
+      <c r="D154" t="s">
         <v>179</v>
-      </c>
-      <c r="C154" t="s">
-        <v>30</v>
-      </c>
-      <c r="D154" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B155" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="C155" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="D155" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="B158" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="C158" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D158" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B159" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C159" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D159" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="B162" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="C162" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D162" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="B165" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="C165" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D165" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B166" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C166" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D166" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="B169" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="C169" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D169" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="B172" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="C172" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D172" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="B175" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="C175" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D175" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="B178" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="C178" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D178" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="B181" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="C181" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D181" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
